--- a/expert-system/output/sick-leave/sick-leave.xlsx
+++ b/expert-system/output/sick-leave/sick-leave.xlsx
@@ -16,6 +16,7 @@
     <sheet name="TS-SL-Permissions" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="TS-SL-Validation" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="TS-SL-APIErrors" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Test Data" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Feature Matrix'!$A$1:$I$8</definedName>
@@ -34,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,8 +87,12 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -136,8 +141,14 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+        <bgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -159,11 +170,55 @@
         <color rgb="00B4C6E7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -210,6 +265,15 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -576,7 +640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A63"/>
+  <dimension ref="A1:A65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -985,6 +1049,13 @@
       <c r="A63" s="7" t="inlineStr">
         <is>
           <t>Total: 120 test cases across 6 test suites</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Test Data Reference</t>
         </is>
       </c>
     </row>
@@ -996,6 +1067,759 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId7"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00BF8F00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sick Leave Module Test Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>&lt;- Back to Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>1. Recommended Test Users (Module-Specific)</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="n"/>
+      <c r="C4" s="24" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>User / Query</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Use Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Use alsmirnov</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>EMPLOYEE</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Create sick leaves as regular employee</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Use kcherenkov</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>View team sick leaves as manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Use ilnitsky</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Process sick leave accounting status</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>2. Common Multi-Role Test Users (All Modules)</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="24" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Best For</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>perekrest</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, CHIEF_ACCOUNTANT, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Best multi-role user (7 roles). Use for cross-role permission testing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>pvaynmaster</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, CHIEF_OFFICER, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Multi-role with CHIEF_OFFICER. Use for highest-privilege scenarios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>ilnitsky</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Admin+accountant combo. Use for accounting and admin tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Same role set as ilnitsky. Use as second admin/accountant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>juliet_nekhor</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>DEPT_MGR, EMPLOYEE, HR, PM, VIEW_ALL</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Has VIEW_ALL. Use for read-only permission tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>kcherenkov</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>DEPT_MGR, EMPLOYEE, PM, TECH_LEAD</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Tech Lead + PM. Use for planner/project management tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>alsmirnov</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>EMPLOYEE</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>EMPLOYEE-only. Use as minimum-privilege baseline user.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>3. Common SQL Queries (User Discovery)</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="24" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>SQL Query</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Find EMPLOYEE-only users (minimum privilege)</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true
+GROUP BY e.id
+HAVING COUNT(*) = 1 AND MAX(r.role) = 'ROLE_EMPLOYEE'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Find active contractors</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_CONTRACTOR'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Find active project managers</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_PROJECT_MANAGER'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Find active accountants</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_ACCOUNTANT'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Find active admins</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_ADMIN'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Get current report/approve periods per office</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>SELECT o.id as office_id, o.name,
+       rp.start as report_period_start,
+       ap.start as approve_period_start
+FROM office o
+JOIN office_period rp ON o.report_period_id = rp.id
+JOIN office_period ap ON o.approve_period_id = ap.id
+ORDER BY o.id;</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>ttt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>4. Module-Specific SQL Queries</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="n"/>
+      <c r="C29" s="24" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>SQL Query</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Find employees without active sick leaves (for create tests)</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>SELECT e.login
+FROM ttt_backend.employee e
+WHERE e.enabled = true
+AND e.login NOT IN (
+  SELECT sl.login FROM ttt_vacation.sick_leave sl
+  WHERE sl.status = 'OPEN' AND sl.end_date &gt;= CURRENT_DATE
+)
+LIMIT 10;</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Find OPEN sick leaves (for close/accounting tests)</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>SELECT sl.id, sl.login, sl.start_date, sl.end_date, sl.status, sl.accounting_status
+FROM ttt_vacation.sick_leave sl
+WHERE sl.status = 'OPEN'
+ORDER BY sl.start_date DESC;</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Find sick leaves by accounting status (for status transition tests)</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>SELECT sl.id, sl.login, sl.status, sl.accounting_status, sl.number
+FROM ttt_vacation.sick_leave sl
+WHERE sl.accounting_status IN ('NEW', 'PAID')
+ORDER BY sl.accounting_status, sl.id;</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>Count sick leaves with attachments</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>SELECT sl.id, sl.login, COUNT(a.id) as attachment_count
+FROM ttt_vacation.sick_leave sl
+LEFT JOIN ttt_vacation.sick_leave_attachment a ON sl.id = a.sick_leave_id
+GROUP BY sl.id, sl.login
+HAVING COUNT(a.id) &gt; 0
+LIMIT 10;</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>5. Data Generation Strategies</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="n"/>
+      <c r="C36" s="24" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Date range</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>startDate: CURRENT_DATE - 3 days, endDate: CURRENT_DATE. Sick leaves are typically retroactive.</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>Number field</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Required for CLOSE. Use format: 'SL-YYYY-NNN' or any unique string.</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Force flag</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>force=false for normal path; force=true to bypass overlap checks.</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>Boundary values</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Same day (1-day), cross-month, overlapping existing sick leave.</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>6. Environment Reference</t>
+        </is>
+      </c>
+      <c r="B43" s="23" t="n"/>
+      <c r="C43" s="24" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>timemachine</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>https://ttt-timemachine.noveogroup.com</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Primary dev env — has test clock (PATCH to advance time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>qa-1</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>https://ttt-qa-1.noveogroup.com</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>Secondary dev env — real clock</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>https://ttt-stage.noveogroup.com</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Production-like env — read-only testing preferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>7. API Authentication</t>
+        </is>
+      </c>
+      <c r="B49" s="23" t="n"/>
+      <c r="C49" s="24" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>How to Obtain/Use</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>JWT (user context)</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>Login via CAS SSO at /login, extract TTT_JWT_TOKEN cookie. Pass as Authorization: Bearer &lt;token&gt; or Cookie header.</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Most endpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>API token</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>Set header API_SECRET_TOKEN: &lt;token_value&gt;. Value from env config file.</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>Test/sync endpoints, limited scope</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A20:C20"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1008,7 +1832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1023,288 +1847,296 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>← Back to Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Feature Area</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>Bug Verification</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>Test Suite</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Lifecycle (CRUD/Files/Notify)</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B3" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C3" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D2" s="9" t="n">
+      <c r="D3" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E2" s="9" t="n">
+      <c r="E3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="9" t="n">
+      <c r="F3" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G2" s="9" t="n">
+      <c r="G3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="9" t="n">
+      <c r="H3" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>TS-SL-Lifecycle</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Dual Status Model</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n">
+      <c r="B4" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C4" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D4" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E4" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F4" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="G3" s="11" t="n">
+      <c r="G4" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="11" t="n">
+      <c r="H4" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>TS-SL-DualStatus</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Accounting Workflow</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B5" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="9" t="n">
+      <c r="H5" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>TS-SL-Accounting</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Permissions &amp; Security</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B6" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C6" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E6" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F6" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H6" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>TS-SL-Permissions</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Validation &amp; Form Rules</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B7" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="H7" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>TS-SL-Validation</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>API Errors &amp; Edge Cases</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B8" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C8" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F8" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="H8" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>TS-SL-APIErrors</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B9" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C9" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D9" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E9" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F9" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <v>120</v>
       </c>
-      <c r="I8" s="14" t="n"/>
+      <c r="I9" s="14" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I8"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1317,7 +2149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1329,416 +2161,423 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>← Back to Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>Likelihood</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>Mitigation / Test Focus</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Dual status model complexity</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Accounting status drives main lifecycle status via coupling rules. PAID-&gt;CLOSED, REJECTED-&gt;REJECTED, NEW/PROCESSING-&gt;OPEN. Complexity leads to unexpected state combinations.</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Test all 16 accounting-&gt;main status transitions. Verify coupling consistency. Test backward transitions.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Missing delete authorization</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>No owner check and no PM check on delete endpoint. Any AUTHENTICATED_USER can delete any non-PAID sick leave. Contrast: update path correctly checks PM relationship.</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Test delete as unrelated user, unrelated PM. Verify only PAID guard exists.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Status reversal (NEW after PAID reverts to OPEN)</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Accounting status can be changed from PAID back to NEW. Coupling rule forces main status from CLOSED back to OPEN. Entire lifecycle reversed with no guardrails.</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Change PAID-&gt;NEW, verify main CLOSED-&gt;OPEN. Document full reversal path.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>No backend MIME validation on file upload</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Only frontend checks file types (PDF, PNG, JPEG). Backend accepts any file via direct API call. Potential vector for malicious file upload.</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Upload .exe, .html, .js files via curl. Verify no server-side MIME check.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Notification bug (identity comparison)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>getEditorType() uses == (reference equality) instead of .equals() on JPA entities. Self-edits always classified as ACCOUNTANT/SUPERVISOR. Wrong notification template variant sent.</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Create as employee, check if OPEN or OPEN_BY_SUPERVISOR template used.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Orphaned records on soft-delete</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Soft delete sets status=DELETED but does NOT clean up sick_leave_file and sick_leave_notify_also junction records. DB accumulates orphaned references.</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Delete sick leave with files. Query DB for remaining junction records.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>SCHEDULED/OVERDUE asymmetry (read-only computed statuses)</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>SCHEDULED and OVERDUE returned in GET responses but not accepted in PATCH requests. SickLeavePatchRequestStatusTypeDTO only has OPEN/CLOSED. Confusing API contract.</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>PATCH with status=SCHEDULED, verify rejection. Document asymmetry.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Shared VacationSecurityException for sick leave</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Sick leave operations throw exception.vacation.no.permission (VacationSecurityException). Same error code used for both modules. Confusing error attribution in logs and responses.</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Trigger VacationSecurityException via sick leave update. Verify error code says 'vacation'.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Force flag NPE risk on patch</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>force is @NotNull Boolean on CreateDTO. PatchDTO inherits it. If force=null somehow reaches service layer, NPE on unboxing. Currently guarded by bean validation but inheritance is fragile.</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>PATCH without force field. Verify @NotNull catches it.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Frontend-only number length limit</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Frontend Yup validates number max 40 chars. Backend has @Size(max=40) on DTO. But if bypassed at DTO level, no DB column length constraint check.</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Send 41-char number via API. Verify @Size rejects. Send 40-char to confirm boundary.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Manager force=true bypass eliminates overlap validation</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Manager create hardcodes force=true in frontend saga. Client-side overlap check capped at 100 records. Combined: managers have zero overlap validation.</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>Manager creates overlapping sick leave. Verify no conflict shown. Monitor API request for force=true.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>API token exclusion from CRUD endpoints</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Sick leave CRUD requires AUTHENTICATED_USER (JWT only). API tokens with 21 permissions get 403. Only search and count endpoints work with tokens.</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Test all CRUD endpoints with API_SECRET_TOKEN header. Verify all return 403.</t>
         </is>
@@ -1746,6 +2585,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F13"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
